--- a/Data/Output/Logs.xlsx
+++ b/Data/Output/Logs.xlsx
@@ -31,10 +31,10 @@
     <x:t>ErrorMessage</x:t>
   </x:si>
   <x:si>
-    <x:t>Service Desk Support</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-15 04:13:57</x:t>
+    <x:t>duongduy12318@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-15 14:03:27</x:t>
   </x:si>
   <x:si>
     <x:t>Success</x:t>
@@ -49,10 +49,31 @@
     <x:t>Japanese Comtor,Java Developer,Service Desk Support,Project Manager,Software Test Engineer,Salesforce Engineer</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-04-15 03:15:19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duongduy12318@gmail.com</x:t>
+    <x:t>2026-04-15 13:29:37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>quocuonguyen12345@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-15 13:29:42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lehuudai611@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-15 13:29:47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khang17122005@GMAIL.COM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-15 13:29:53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kinhbui2003@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-15 13:29:59</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -429,10 +450,10 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
         <x:v>6</x:v>
@@ -458,6 +479,74 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:5">
+      <x:c r="A4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5">
+      <x:c r="A5" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5">
+      <x:c r="A6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:5">
+      <x:c r="A7" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>

--- a/Data/Output/Logs.xlsx
+++ b/Data/Output/Logs.xlsx
@@ -34,7 +34,10 @@
     <x:t>duongduy12318@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-04-15 14:03:27</x:t>
+    <x:t>2026-04-15 16:07:11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-15 16:06:44</x:t>
   </x:si>
   <x:si>
     <x:t>Success</x:t>
@@ -46,34 +49,31 @@
     <x:t>duongduy12317@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>Japanese Comtor,Java Developer,Service Desk Support,Project Manager,Software Test Engineer,Salesforce Engineer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-15 13:29:37</x:t>
+    <x:t>2026-04-15 16:06:52</x:t>
   </x:si>
   <x:si>
     <x:t>quocuonguyen12345@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-04-15 13:29:42</x:t>
+    <x:t>2026-04-15 16:06:58</x:t>
   </x:si>
   <x:si>
     <x:t>lehuudai611@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-04-15 13:29:47</x:t>
+    <x:t>2026-04-15 16:07:05</x:t>
   </x:si>
   <x:si>
     <x:t>khang17122005@GMAIL.COM</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-04-15 13:29:53</x:t>
-  </x:si>
-  <x:si>
     <x:t>kinhbui2003@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-04-15 13:29:59</x:t>
+    <x:t>Japanese Comtor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-15 16:06:37</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -453,33 +453,33 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
         <x:v>9</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
@@ -487,16 +487,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
@@ -504,16 +504,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
@@ -521,33 +521,33 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/Output/Logs.xlsx
+++ b/Data/Output/Logs.xlsx
@@ -31,49 +31,49 @@
     <x:t>ErrorMessage</x:t>
   </x:si>
   <x:si>
-    <x:t>duongduy12318@gmail.com</x:t>
+    <x:t>2026-04-15 17:07:21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Japanese Comtor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Success</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>duongduy12317@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-15 16:06:44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>quocuonguyen12345@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-15 16:06:52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lehuudai611@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-15 16:06:58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khang17122005@GMAIL.COM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-15 16:07:05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kinhbui2003@gmail.com</x:t>
   </x:si>
   <x:si>
     <x:t>2026-04-15 16:07:11</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-04-15 16:06:44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Success</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>duongduy12317@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-15 16:06:52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>quocuonguyen12345@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-15 16:06:58</x:t>
-  </x:si>
-  <x:si>
-    <x:t>lehuudai611@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-15 16:07:05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>khang17122005@GMAIL.COM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>kinhbui2003@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Japanese Comtor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-15 16:06:37</x:t>
+    <x:t>duongduy12314@Gmail.com</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -450,87 +450,87 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="D2" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="D3" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="E3" s="0" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="D4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="D5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="D6" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
@@ -538,16 +538,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="D7" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>9</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
